--- a/testdata/BidDetailsDataGUJRAT.xlsx.xlsx
+++ b/testdata/BidDetailsDataGUJRAT.xlsx.xlsx
@@ -12,9 +12,9 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="true"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -76,6 +76,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -451,15 +452,15 @@
   <dimension ref="A1:AL4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="13.42578125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="3" customWidth="1"/>
-    <col min="7" max="8" width="12" style="3" customWidth="1"/>
-    <col min="9" max="11" width="10.28515625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="3" customWidth="true" style="3" width="13.42578125"/>
+    <col min="4" max="4" customWidth="true" style="3" width="14.42578125"/>
+    <col min="5" max="5" customWidth="true" style="3" width="13.42578125"/>
+    <col min="6" max="6" customWidth="true" style="3" width="11.5703125"/>
+    <col min="7" max="8" customWidth="true" style="3" width="12.0"/>
+    <col min="9" max="11" customWidth="true" style="3" width="10.28515625"/>
+    <col min="12" max="12" customWidth="true" style="3" width="10.85546875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="3" width="11.28515625"/>
+    <col min="14" max="16384" style="3" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="90" x14ac:dyDescent="0.25">
@@ -526,34 +527,34 @@
       <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3">
-        <v>1828010761.3800001</v>
-      </c>
-      <c r="E2" s="3">
-        <v>13077124.34</v>
+      <c r="D2" s="3" t="n">
+        <v>1.82801031318E9</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1.307712434E7</v>
       </c>
       <c r="F2" s="3">
-        <v>123</v>
+        <v>1011</v>
       </c>
       <c r="G2" s="3">
-        <v>100</v>
-      </c>
-      <c r="H2" s="3">
-        <v>60424.800000000003</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1827950336.5799999</v>
-      </c>
-      <c r="J2" s="3">
-        <v>13137549.140000001</v>
+        <v>500</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>1516500.0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>1.82649381318E9</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>1.459362434E7</v>
       </c>
       <c r="L2" s="3">
         <f>D2-I2</f>
-        <v>60424.800000190735</v>
+        <v>150300</v>
       </c>
       <c r="M2" s="3">
         <f>J2-E2</f>
-        <v>60424.800000000745</v>
+        <v>150300</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
@@ -589,26 +590,26 @@
       <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3">
-        <v>168466040.02000001</v>
-      </c>
-      <c r="E3" s="3">
-        <v>10011197.880000001</v>
+      <c r="D3" s="3" t="n">
+        <v>1.6846604002E8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1.001119788E7</v>
       </c>
       <c r="F3" s="3">
-        <v>124</v>
+        <v>1012</v>
       </c>
       <c r="G3" s="3">
-        <v>100</v>
-      </c>
-      <c r="H3" s="3">
-        <v>60928.34</v>
-      </c>
-      <c r="I3" s="3">
-        <v>168405111.72</v>
-      </c>
-      <c r="J3" s="3">
-        <v>10072126.18</v>
+        <v>500</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1518000.0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>1.6694804002E8</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>1.152919788E7</v>
       </c>
       <c r="L3" s="3">
         <f>D3-I3</f>
@@ -629,26 +630,26 @@
       <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="3">
-        <v>1033065086.78</v>
-      </c>
-      <c r="E4" s="3">
-        <v>9093507.2799999993</v>
+      <c r="D4" s="3" t="n">
+        <v>1.03238749822E9</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9764046.28</v>
       </c>
       <c r="F4" s="3">
-        <v>125</v>
+        <v>1013</v>
       </c>
       <c r="G4" s="3">
-        <v>100</v>
-      </c>
-      <c r="H4" s="3">
-        <v>61431.88</v>
-      </c>
-      <c r="I4" s="3">
-        <v>1033003654.88</v>
-      </c>
-      <c r="J4" s="3">
-        <v>9154939.1799999997</v>
+        <v>500</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1519500.0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1.03086799822E9</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1.128354628E7</v>
       </c>
       <c r="L4" s="3">
         <f>D4-I4</f>
